--- a/data/trans_orig/Q5402-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2007</t>
+          <t>Población según si son capaces de prepararse la comida en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>33492</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57620</t>
+          <t>57289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69387</t>
+          <t>69409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46975</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59472</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82661</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94055</t>
+          <t>93891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133234</t>
+          <t>133561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150960</t>
+          <t>150882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49159</t>
+          <t>49123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>63631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76766</t>
+          <t>76859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109395</t>
+          <t>108658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124603</t>
+          <t>124611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52474</t>
+          <t>52445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52618</t>
+          <t>52704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66564</t>
+          <t>66722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100439</t>
+          <t>100702</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116207</t>
+          <t>116939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26746</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47129</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60679</t>
+          <t>60626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29225</t>
+          <t>29130</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40718</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56292</t>
+          <t>55112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67720</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89040</t>
+          <t>89750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,47 +3484,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2917</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2917</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8377</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24972</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90832</t>
+          <t>91169</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102342</t>
+          <t>102431</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>97500</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>110949</t>
+          <t>110067</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>192177</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>209997</t>
+          <t>210846</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>21375</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>33132</t>
+          <t>34647</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>85635</t>
+          <t>86426</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>100878</t>
+          <t>100785</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>123522</t>
+          <t>124544</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>141282</t>
+          <t>142002</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>216969</t>
+          <t>216343</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>238676</t>
+          <t>238260</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>36846</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>80333</t>
+          <t>79749</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>62298</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>78899</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>117050</t>
+          <t>115365</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>412889</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>443373</t>
+          <t>443230</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>572581</t>
+          <t>571453</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>608600</t>
+          <t>607620</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>998075</t>
+          <t>994367</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1043331</t>
+          <t>1041130</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2012</t>
+          <t>Población según si son capaces de prepararse la comida en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37716</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>39107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56501</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73973</t>
+          <t>74983</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34449</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30710</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>51785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68669</t>
+          <t>68666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70602</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87807</t>
+          <t>87739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127052</t>
+          <t>128432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152559</t>
+          <t>153042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54780</t>
+          <t>54941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>69474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94550</t>
+          <t>93482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114318</t>
+          <t>114350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>27384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>52101</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57476</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73189</t>
+          <t>73992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99607</t>
+          <t>101780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121858</t>
+          <t>122672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>41531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52377</t>
+          <t>52531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14690</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>24832</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43097</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45348</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>59641</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79282</t>
+          <t>79300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99430</t>
+          <t>98312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79796</t>
+          <t>80762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>98919</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>105243</t>
+          <t>105055</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>125083</t>
+          <t>123996</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>191187</t>
+          <t>191661</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>218081</t>
+          <t>218312</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>94909</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113061</t>
+          <t>111907</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>131615</t>
+          <t>133842</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>150900</t>
+          <t>150866</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>234183</t>
+          <t>233557</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>259359</t>
+          <t>259170</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>41497</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70429</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>94950</t>
+          <t>95538</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>109837</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>156254</t>
+          <t>156214</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83806</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>60221</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>94618</t>
+          <t>94463</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>117651</t>
+          <t>120702</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>168529</t>
+          <t>167168</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>416624</t>
+          <t>417477</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>458060</t>
+          <t>459168</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>567038</t>
+          <t>564794</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>613058</t>
+          <t>612081</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>998509</t>
+          <t>998660</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1061398</t>
+          <t>1062279</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2016</t>
+          <t>Población según si son capaces de prepararse la comida en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>809</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>29868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>43375</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75534</t>
+          <t>75598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70415</t>
+          <t>69021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81729</t>
+          <t>81278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89832</t>
+          <t>89005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107119</t>
+          <t>107009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165217</t>
+          <t>164527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185265</t>
+          <t>185745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60486</t>
+          <t>60388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66075</t>
+          <t>65912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78620</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121115</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136667</t>
+          <t>136915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45426</t>
+          <t>46066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>57117</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68115</t>
+          <t>68378</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85490</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120038</t>
+          <t>120002</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139509</t>
+          <t>139567</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25691</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40471</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40598</t>
+          <t>41037</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63527</t>
+          <t>63297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79762</t>
+          <t>79518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20396</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29493</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>40522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>45083</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60865</t>
+          <t>60536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80236</t>
+          <t>79505</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99264</t>
+          <t>97832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>25934</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>18659</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26982</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85520</t>
+          <t>85443</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>101128</t>
+          <t>100922</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>111285</t>
+          <t>111710</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>131214</t>
+          <t>131373</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>202866</t>
+          <t>203521</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>228510</t>
+          <t>228564</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>26651</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>115100</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>128354</t>
+          <t>128559</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>143030</t>
+          <t>142568</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>164003</t>
+          <t>163992</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>265129</t>
+          <t>264910</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>289337</t>
+          <t>289196</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>106613</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>61979</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>54947</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>93122</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,47 +13224,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>118919</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>96723</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>141925</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>118919</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>99039</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>142262</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>491258</t>
+          <t>491916</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>522793</t>
+          <t>522488</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>633936</t>
+          <t>631389</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>679766</t>
+          <t>678434</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1135936</t>
+          <t>1134626</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1192566</t>
+          <t>1193388</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2023</t>
+          <t>Población según si son capaces de prepararse la comida en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44398</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53977</t>
+          <t>53992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81679</t>
+          <t>81213</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96147</t>
+          <t>95914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>62483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73957</t>
+          <t>73697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93599</t>
+          <t>92583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107859</t>
+          <t>107413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160722</t>
+          <t>160941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178818</t>
+          <t>178845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20681</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>46984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>58973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57160</t>
+          <t>57278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69930</t>
+          <t>69518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108874</t>
+          <t>109141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125379</t>
+          <t>125149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53734</t>
+          <t>54194</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64826</t>
+          <t>64992</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78534</t>
+          <t>78275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88666</t>
+          <t>87930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136675</t>
+          <t>134939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>150998</t>
+          <t>150330</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41145</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49155</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66649</t>
+          <t>66140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46309</t>
+          <t>45522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77423</t>
+          <t>77312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>90241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>39661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105321</t>
+          <t>105756</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116660</t>
+          <t>116477</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>269509</t>
+          <t>269331</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>333205</t>
+          <t>333477</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,17 +16780,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>425363</t>
+          <t>425364</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>392162</t>
+          <t>391646</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>450351</t>
+          <t>450052</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15247</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>29095</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>47107</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>126713</t>
+          <t>126920</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>137843</t>
+          <t>138100</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>147277</t>
+          <t>145618</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>161485</t>
+          <t>161887</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>276919</t>
+          <t>278184</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>296198</t>
+          <t>297029</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>59154</t>
+          <t>59650</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>39638</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>98487</t>
+          <t>99158</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>80152</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>149074</t>
+          <t>147471</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52112</t>
+          <t>52417</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>74898</t>
+          <t>76764</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58735</t>
+          <t>57215</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>135842</t>
+          <t>135659</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>110155</t>
+          <t>108064</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>196453</t>
+          <t>198804</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>522579</t>
+          <t>519871</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>550950</t>
+          <t>549743</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>803025</t>
+          <t>801896</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>935986</t>
+          <t>934419</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1341421</t>
+          <t>1342454</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1487986</t>
+          <t>1498299</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
